--- a/三峡项目/2026-09-28/三峡融担_保后检查策略部署落地方案_V27.xlsx
+++ b/三峡项目/2026-09-28/三峡融担_保后检查策略部署落地方案_V27.xlsx
@@ -2182,7 +2182,7 @@
     <col width="21.925" customWidth="1" min="4" max="4"/>
     <col width="18.65" customWidth="1" min="5" max="5"/>
     <col width="9.616666666666671" customWidth="1" min="6" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I2" s="40" t="inlineStr">
         <is>
-          <t>编排主策略——内含企业/个人/关联企业三个集合循环子策略节点(ChildFlowNode round)，按入参数组逐主体调用子策略</t>
+          <t>编排主策略（bhjcpostMain v6 已上线）——内含企业/个人/关联企业三个子策略节点，均 round=false，即单次调用、非集合循环【2026-09-28 graphJson 实测】</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>循环子策略（集合循环），按企业数组逐主体调用；设计推断，待复核</t>
+          <t>单次调用子策略（父策略 ChildFlowNode round=false，非循环）【graphJson 实测】</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
-          <t>循环子策略（集合循环），按个人数组逐主体调用；设计推断，待复核</t>
+          <t>单次调用子策略（父策略 ChildFlowNode round=false，非循环）【graphJson 实测】</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
-          <t>循环子策略（集合循环），按关联企业数组逐主体调用；设计推断，待复核</t>
+          <t>单次调用子策略（父策略 ChildFlowNode round=false，非循环）【graphJson 实测】</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
-          <t>编排主策略，内含集合循环子策略节点；2026-09-28已实测：企业节点round=true、喂2个企业时tokenIds.length=2、逐元素起子token</t>
+          <t>编排主策略（bhjcpostMainBefore v10 已上线）——内含三个集合循环子策略节点，均 round=true【graphJson 实测】</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
-          <t>循环子策略（集合循环）；已实测，tokenIds=2逐元素迭代</t>
+          <t>循环子策略（集合循环 round=true，入参 C_O_ENTERPRISEINFO）【graphJson 实测】；运行时逐元素迭代已实测 tokenIds=2</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
-          <t>循环子策略（集合循环），按个人数组逐主体调用；设计推断，待复核（测试数据仅喂1元素，无法与单次调用区分）</t>
+          <t>循环子策略（集合循环 round=true，入参 C_O_PERSONINFO）【graphJson 实测】；运行时逐元素迭代待复核（测试数据仅喂1元素，无法与单次调用区分）</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
-          <t>循环子策略（集合循环），按关联企业数组逐主体调用；设计推断，待复核（同上，1元素不可区分）</t>
+          <t>循环子策略（集合循环 round=true，入参 C_O_RELATEDCOMPANYINFO）【graphJson 实测】；运行时逐元素迭代待复核（同上，1元素不可区分）</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
     <row r="13">
       <c r="A13" s="51" t="inlineStr">
         <is>
-          <t>备注：本列"循环子策略"指平台按入参数组逐元素起子token的集合循环(ChildFlowNode round=true)，与"函数"sheet中股东/持股公司循环函数(脚本内部下标循环)不同；"已实测"依据2026-09-28 sxdb bhjcpostMainBefore v10 取证，"待复核"为设计推断，须以平台graphJson实时复核为准。</t>
+          <t>备注：本列"循环子策略"指平台按入参数组逐元素起子token的集合循环(父策略 ChildFlowNode 的 attributes.round=true)，与"函数"sheet中股东/持股公司循环函数(脚本内部下标循环)不同。【2026-09-28 经 sxdb graphJson 实测】：贷中 bhjcpostMain v6 三个子策略节点 round=false（单次调用），贷前 bhjcpostMainBefore v10 三个节点 round=true（集合循环）；同名子策略因父策略版本不同而执行方式不同。贷前企业节点另经运行时取证坐实逐元素迭代(tokenIds=2)，个人/关联企业仅设计层 round=true、运行时迭代待复核。</t>
         </is>
       </c>
     </row>
